--- a/backend/recipe_cache.xlsx
+++ b/backend/recipe_cache.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1072,6 +1072,54 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>4a53be1c830e74f70fabd1b8e0f87e30fe31acdbc119752e410dca4815c7dbb0</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>one slice of whole wheat toast</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Recipe: One Slice of Whole Wheat Toast
+Brief Description: A simple and delicious slice of whole wheat toast, perfect for breakfast or as a side dish.
+Ingredients:
+* 1 slice of whole wheat bread (about 20-25 g)
+* 1 tablespoon (15 ml) of butter or margarine
+* Salt and pepper to taste
+Step-by-Step Cooking Instructions:
+1. Preheat a non-stick skillet or griddle over medium heat.
+2. Butter the bread slice on one side, making sure to cover the entire surface.
+3. Place the bread slice, buttered side down, in the skillet.
+4. Cook for about 2-3 minutes, or until the bread is golden brown and the bottom is crispy.
+5. Use a spatula to carefully flip the bread over and cook for an additional 1-2 minutes, or until the other side is also golden brown.
+6. Remove the toast from the skillet and season with salt and pepper to taste.
+7. Serve immediately and enjoy!
+Prep Time: 5 minutes
+Cook Time: 5-7 minutes
+Servings: 1 slice
+Cooking Tips:
+* Use a non-stick skillet or griddle to prevent the bread from sticking.
+* Adjust the heat as needed to achieve a golden brown color on both sides of the bread.
+* If you prefer a crisper crust, cook the bread for a shorter amount of time. If you prefer a softer crust, cook it for a longer amount of time.
+* You can also add other toppings such as avocado, tomatoes, or hummus to make the toast more interesting.
+* If you don't have whole wheat bread, you can use any other type of bread you prefer. Just adjust the cooking time accordingly.
+Substitution Suggestions:
+* Use a different type of fat such as olive oil or coconut oil instead of butter or margarine.
+* Experiment with different types of bread, such as whole wheat, white, or sourdough.
+* Add other toppings such as cheese, nuts, or fruit to make the toast more substantial.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-06-06 16:12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
